--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1598,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1663,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1728,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1793,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1980,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2045,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2110,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2175,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2240,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2305,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2431,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2496,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2561,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2626,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2752,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2817,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2882,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
